--- a/ai_logs/Đoàn Mạnh Đạt AI log.xlsx
+++ b/ai_logs/Đoàn Mạnh Đạt AI log.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="261">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -1004,6 +1004,21 @@
   </si>
   <si>
     <t>Great idea</t>
+  </si>
+  <si>
+    <t>bắt đầu code Viết CsvRepository&lt;T&gt; generic abstract, Viết EmployeeRepository, Viết DepartmentRepository , Test đọc 12k dòng attendance &lt; 1 giây</t>
+  </si>
+  <si>
+    <t>hảy code cho tôi  1. Viết CsvRepository&lt;T&gt; generic abstract $\star$ ưu tiên số 1Lớp cha của tất cả repository. Dùng Generic &lt;T BaseEntity extends&gt;. Viết xong trong ngày 1 rồi push Git ngay cho 3 người kia pull về.CsvRepository.java $\star$ viết trước nhất2. Viết EmployeeRepositoryKế thừa CsvRepository. Thêm: findByDepartment(), findByType(), searchByName(). Simulator cần findByDepartment() để tạo HR Thread.EmployeeRepository.java3. Viết DepartmentRepositoryĐơn giản nhất — chỉ cần CRUD + findByName(). Simulator cần findAll() để biết có bao nhiêu phòng ban.DepartmentRepository.java4. Test đọc 12k dòng attendance &lt; 1 giâyRubric yêu cầu: đọc 12,000 dòng attendance.csv phải xong trong dưới 1 giây. Dùng BufferedReader thay Scanner để đảm bảo hiệu năng.PerformanceTest.java $\star$ rubric yêu cầu&lt;/T&gt;&lt;/T&gt;</t>
+  </si>
+  <si>
+    <t>tạo file CsvRepository , EmployeeRepository , DepartmentRepository ,   PerformanceTest .</t>
+  </si>
+  <si>
+    <t>Critical Thinking: chưa biết T entity trong đó có ý nghĩa gì và cách hoạt động của performanceTest.
+Contextualization: không có .
+Creative Synthesis: tôi quyết định tìm hiểu.
+Decision: hỏi ai cách hoạt động của cả hai.</t>
   </si>
 </sst>
 </file>
@@ -1918,13 +1933,27 @@
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+      <c r="A8" s="7">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>260</v>
+      </c>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/ai_logs/Đoàn Mạnh Đạt AI log.xlsx
+++ b/ai_logs/Đoàn Mạnh Đạt AI log.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="277">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -1015,10 +1015,81 @@
     <t>tạo file CsvRepository , EmployeeRepository , DepartmentRepository ,   PerformanceTest .</t>
   </si>
   <si>
+    <t xml:space="preserve">thiết kế lại attendanceCSVRepositoryTest </t>
+  </si>
+  <si>
+    <t xml:space="preserve">hảy thiết kế lại attendanceCSVRepositoryTest thay vì đếm số dòng của file attendance .csv mà hảy thiết kế attendanceCSVRepositoryTest là nời bạn đọc hết tất cả dử liệu tư folder data xem tổng cộng từng file có bao nhiêu và nều thiếu bất kỳ phần nào thì nó sẻ in ra màng hình thiếu cái này và nó nằm ở đâu dòng nào </t>
+  </si>
+  <si>
+    <t>1 Quét toàn bộ thư mục dữ liệu               2Xác định cấu trúc &amp; đếm dòng dữ liệu         3Phát hiện và báo cáo các phần bị thiếu (Missing fields/columns)                                      4Hạ phiên bản Java Compile trong pom.xml từ 21 xuống 17.</t>
+  </si>
+  <si>
     <t>Critical Thinking: chưa biết T entity trong đó có ý nghĩa gì và cách hoạt động của performanceTest.
 Contextualization: không có .
 Creative Synthesis: tôi quyết định tìm hiểu.
-Decision: hỏi ai cách hoạt động của cả hai.</t>
+Decision: hỏi AI cách hoạt động của cả hai.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: nó có thể biết ở đâu nhưng lại không biết thay đổi đó là gì.
+Contextualization: khi bạn sửa đổi nhửng gì bạn cần biết bạn đã chuyển thành gì để xem có đúng chưa  .
+Creative Synthesis: thêm chức năng có thể xác định thay đổi .
+Decision: thêm chức năng có thể xác định thay đổi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> thêm chức năng có thể xác định thay đổi gì  cho attendanceCSVRepositoryTest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bạn có thể thiết kế thêm cho tôi chức năng mới nơi attendanceCSVRepositoryTest có thể xác định việc bạn đã thay đổi gì ở folder data trong bất kì file gì trong đó và xác định xem bạn đã thay đổi gì và so sánh xem với file chưa thay đổi xem điểm khác nhau là gì </t>
+  </si>
+  <si>
+    <t xml:space="preserve">làm sao để chức năng mới chập thuận sự thay đổi của file </t>
+  </si>
+  <si>
+    <t>hãy thêm khả năng giới hạn thời gian trong việc đọc tất cả file trong folder data trong tầm 1 giây</t>
+  </si>
+  <si>
+    <t>1Đo thời gian bắt đầu và kết thúc (Timing): Dùng System.nanoTime() bao quanh quá trình tìm kiếm, đọc dữ liệu, phân tích dòng/cột, và kiểm thử giá trị trống của tất cả các file CSV trong thư mục data/.
+2In thống kê thời gian và giới hạn:
+In ra console tổng thời gian xử lý: Total processing time: X ms (Limit: &lt; 1000 ms).
+3Assertion đảm bảo hiệu năng:
+Thêm câu lệnh assertTrue(elapsedMs &lt; 1000.0, ...) để tự động đánh dấu kiểm thử thất bại nếu thời gian xử lý vượt quá 1 giây (1000 ms).</t>
+  </si>
+  <si>
+    <t>Để chức năng kiểm thử chấp thuận (accept/update) sự thay đổi của file và thiết lập các file mới làm baseline (mốc so sánh mới), tôi đã thiết kế 2 cách rất đơn giản và linh hoạt</t>
+  </si>
+  <si>
+    <t>Tạo baseline copy (data_backup/):
+Trong lần chạy kiểm thử đầu tiên, hệ thống sẽ tự động tạo một thư mục backup tên là data_backup và sao chép toàn bộ các file CSV nguyên bản sang đó làm điểm đối chiếu chuẩn (baseline).
+Xác định các thay đổi trong bất kì file CSV nào:
+So sánh danh sách các file giữa thư mục data/ hiện tại và data_backup/ để nhận diện file bị thêm mới hoặc xóa bỏ.
+Đối với các file tồn tại ở cả hai thư mục, hệ thống sẽ thực hiện kiểm tra sâu (deep comparison) ở mức độ bản ghi bằng cách ánh xạ khóa chính (ID của từng dòng):
+Thêm mới (Added Record): Phát hiện dòng dữ liệu mới được thêm, ghi nhận nội dung và số dòng cụ thể ở file hiện tại.
+Xóa bỏ (Deleted Record): Phát hiện dòng dữ liệu cũ đã bị xóa, ghi nhận số dòng trước đó trong file backup.
+Sửa đổi (Modified Record): Đối chiếu chi tiết từng cột/trường dữ liệu giữa hai phiên bản để in ra chính xác trường nào đã thay đổi giá trị từ gì sang gì.</t>
+  </si>
+  <si>
+    <t>muốn attendanceCSVRepositoryTest chấp thuận sự thay đổi</t>
+  </si>
+  <si>
+    <t>thêm khả năng giới hạn thời gian</t>
+  </si>
+  <si>
+    <t>Critical Thinking: biết có thay đổi nhưng không chấp thuận thay đổi .
+Contextualization: khi bạn muốn cập nhập thứ mới thì phải được chấp thuận sự thay đổi  .
+Creative Synthesis: thêm khả năng chấp thuân thay đổi .
+Decision: thêm khả năng chấp thuận thay đổi .</t>
+  </si>
+  <si>
+    <t>Critical Thinking: không biết việc đọc file tốn bao lâu.
+Contextualization: khi bạn đọc file gì thì đều muốn file biết khả năng đọc tối đa trong bao nhiêu thời gian  .
+Creative Synthesis: thêm khả năng giới hạn thời gian.
+Decision: thêm khả năng giới hạn thời gian.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: chưa biết.
+Contextualization: chưa biết   .
+Creative Synthesis: chưa biết .
+Decision: chưa biết .</t>
   </si>
 </sst>
 </file>
@@ -1952,48 +2023,104 @@
         <v>259</v>
       </c>
       <c r="G8" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>264</v>
+      </c>
       <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="A10" s="7">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>274</v>
+      </c>
       <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="A11" s="7">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>275</v>
+      </c>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="A12" s="7">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>276</v>
+      </c>
       <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/ai_logs/Đoàn Mạnh Đạt AI log.xlsx
+++ b/ai_logs/Đoàn Mạnh Đạt AI log.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="280">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -1090,6 +1090,16 @@
 Contextualization: chưa biết   .
 Creative Synthesis: chưa biết .
 Decision: chưa biết .</t>
+  </si>
+  <si>
+    <t>làm phần leavecontroler (submit, approve, reject) , LeaveView (bảng nghỉ phép) và kết nối với LeaveController</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement LeaveController (submit, approve, reject)
+Implement LeaveView (bảng nghỉ phép) và kết nối với LeaveController hãy làm cái này chỉ cái này thôi </t>
+  </si>
+  <si>
+    <t>1. Thay đổi cấu hình dự án                           2. Định nghĩa các ngoại lệ nghiệp vụ tùy chỉnh (Custom Exceptions)                           3. Cài đặt các lớp Controller &amp; View              4. Kiểm thử chất lượng (Unit Testing)</t>
   </si>
 </sst>
 </file>
@@ -2124,13 +2134,27 @@
       <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
+      <c r="A13" s="7">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>276</v>
+      </c>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/ai_logs/Đoàn Mạnh Đạt AI log.xlsx
+++ b/ai_logs/Đoàn Mạnh Đạt AI log.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="283">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -767,193 +767,6 @@
 The class diagrams and MVC structure.
 The strategy for generating $\ge 10,000$ rows of realistic HR data (including attendance.csv $\ge 12,000$ rows).
 The 4 synchronization mechanisms to compare (No Lock, Global Lock, Row Lock, and Optimistic Lock).</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Implementation Plan - Employee Payroll Management Simulation
-This implementation plan outlines the design and development of the **Employee Payroll Management Simulation System** in Java (following the MVC architecture). It addresses the research question on thread synchronization mechanisms when updating leave balances and payroll entries concurrently in a CSV-backed system.
----
-## User Review Required
-&gt; [!IMPORTANT]
-&gt; **Key Decisions &amp; Requirements**:
-&gt; 1. **No Database**: All entities are serialized to and from 7 CSV files.
-&gt; 2. **CSV Row Counts**: `attendance.csv` will contain $\ge 12,000$ lines, representing attendance logs for approximately 500 employees over 24 days. Total database size will exceed 15,000 lines.
-&gt; 3. **Concurrency Simulation**: Multiple thread pools (representing HR processing units) will run concurrently.
-&gt; 4. **Four Locking Mechanisms to Compare**:
-&gt;    - **No Locking (Unsynchronized)**
-&gt;    - **Global Lock (Pessimistic - File/Table Lock)**
-&gt;    - **Fine-Grained Pessimistic Lock (Row/Employee Lock)**
-&gt;    - **Optimistic Locking (Version Check &amp; Retry)**
----
-## Open Questions
-&gt; [!NOTE]
-&gt; None at the moment. The CSV schemas and multi-threading models are fully defined based on the specifications. If any adjustments are needed, they will be refined in the feedback.
----
-## Proposed Changes
-We will create a structured Maven project (or direct Java files if preferred, but a standard Java project structure is cleaner). Let's establish a standard layout under `d:/lab211 t1 final`:
-### Component 1: Data Architecture (CSV Schema Design)
-We will define 7 CSV schemas to support the simulation:
-1. **`departments.csv`**
-   - Columns: `department_id` (String, PK), `name` (String), `manager_id` (String, FK to employees)
-2. **`employees.csv`**
-   - Columns: `employee_id` (String, PK), `first_name` (String), `last_name` (String), `email` (String), `phone` (String), `role` (String), `hire_date` (String, YYYY-MM-DD), `base_salary` (double), `department_id` (String, FK to departments)
-3. **`leave_balances.csv`**
-   - Columns: `leave_balance_id` (String, PK), `employee_id` (String, FK to employees, Unique), `annual_remaining` (int), `sick_remaining` (int), `version` (int)
-4. **`leave_requests.csv`**
-   - Columns: `leave_request_id` (String, PK), `employee_id` (String, FK to employees), `leave_type` (String: `ANNUAL` | `SICK`), `start_date` (String, YYYY-MM-DD), `end_date` (String, YYYY-MM-DD), `requested_days` (int), `status` (String: `PENDING` | `APPROVED` | `REJECTED`), `approved_by` (String, FK to employees), `version` (int)
-5. **`attendance.csv`**
-   - Columns: `attendance_id` (String, PK), `employee_id` (String, FK to employees), `date` (String, YYYY-MM-DD), `check_in_time` (String, HH:MM or empty), `check_out_time` (String, HH:MM or empty), `status` (String: `PRESENT` | `ABSENT` | `LATE` | `EARLY_LEAVE`)
-6. **`payroll_runs.csv`**
-   - Columns: `payroll_run_id` (String, PK), `month_year` (String, MM-YYYY), `status` (String: `PENDING` | `PROCESSING` | `COMPLETED`), `run_by` (String), `created_at` (String, ISO Timestamp), `finished_at` (String, ISO Timestamp or empty)
-7. **`payroll_entries.csv`**
-   - Columns: `payroll_entry_id` (String, PK), `payroll_run_id` (String, FK to payroll_runs), `employee_id` (String, FK to employees), `base_salary` (double), `overtime_hours` (double), `overtime_pay` (double), `deduction_absent` (double), `tax` (double), `net_salary` (double), `status` (String: `PENDING` | `PROCESSED`), `version` (int)
----
-### Component 2: Models &amp; Repositories
-We will write clean Java classes to represent these models and handle CSV I/O using a robust CSV utility class.
-#### [NEW] [Employee.java](file:///d:/lab211%20t1%20final/src/main/java/com/payroll/model/Employee.java)
-- Basic Employee attributes (id, names, email, department, salary).
-#### [NEW] [Department.java](file:///d:/lab211%20t1%20final/src/main/java/com/payroll/model/Department.java)
-- Department attributes (id, name, manager).
-#### [NEW] [LeaveBalance.java](file:///d:/lab211%20t1%20final/src/main/java/com/payroll/model/LeaveBalance.java)
-- Leave balance, including `version` for optimistic locking.
-#### [NEW] [LeaveRequest.java](file:///d:/lab211%20t1%20final/src/main/java/com/payroll/model/LeaveRequest.java)
-- Request details, date range, status, and version.
-#### [NEW] [AttendanceRecord.java](file:///d:/lab211%20t1%20final/src/main/java/com/payroll/model/AttendanceRecord.java)
-- Daily attendance logs.
-#### [NEW] [PayrollRun.java](file:///d:/lab211%20t1%20final/src/main/java/com/payroll/model/PayrollRun.java)
-- Represents a monthly payroll processing execution.
-#### [NEW] [PayrollEntry.java](file:///d:/lab211%20t1%20final/src/main/java/com/payroll/model/PayrollEntry.java)
-- Employee's payroll entry details including `version` for optimistic locking.
-#### [NEW] [CsvRepository.java](file:///d:/lab211%20t1%20final/src/main/java/com/payroll/repository/CsvRepository.java)
-- Generic CSV utility class that reads and writes objects from/to files. We will implement manual serialization/deserialization methods to avoid library dependencies, ensuring high portability and compliance with LAB211 rules.
-#### [NEW] [EmployeeRepository.java](file:///d:/lab211%20t1%20final/src/main/java/com/payroll/repository/EmployeeRepository.java)
-- Employee-specific CSV data access operations.
-#### [NEW] [LeaveRepository.java](file:///d:/lab211%20t1%20final/src/main/java/com/payroll/repository/LeaveRepository.java)
-- Access and update operations for leave balances and requests. Incorporates different synchronization modes (No Lock, Global Lock, Row Lock, Optimistic Lock).
-#### [NEW] [PayrollRepository.java](file:///d:/lab211%20t1%20final/src/main/java/com/payroll/repository/PayrollRepository.java)
-- Access and update operations for payroll runs and entries. Handles concurrency logic.
----
-### Component 3: Data Generator (DataGenerator.java)
-To satisfy the request to generate $\ge 10,000$ rows of realistic HR data:
-#### [NEW] [DataGenerator.java](file:///d:/lab211%20t1%20final/src/main/java/com/payroll/generator/DataGenerator.java)
-- Creates:
-  - 10 departments
-  - 500 employees (evenly distributed)
-  - 500 leave balances (1 per employee)
-  - 1,000 leave requests (some pending, some approved, some rejected)
-  - 12,000+ attendance records (24 working days for 500 employees)
-  - 500 payroll entries for the current month run
-  - 1 payroll run
-- Ensures total row counts exceed 15,000 across all CSVs.
-- Includes a self-check (round-trip test) to parse files back and verify no data fields are lost.
----
-### Component 4: System Architecture (UML &amp; Diagrams)
-Below is the **Use Case Diagram** and **Class Diagram** represented using Mermaid.
-#### Use Case Diagram
-```mermaid
-usecaseDiagram
-    actor HRAdmin as "HR Administrator"
-    actor HRThread as "HR Thread (Simulation)"
-    HRAdmin --&gt; (Generate Test Data)
-    HRAdmin --&gt; (Run Simulator Tool)
-    HRAdmin --&gt; (View Reports &amp; Metrics)
-    HRThread --&gt; (Approve Leave Request)
-    HRThread --&gt; (Process Payroll Entry)
-    HRThread --&gt; (Write to CSV File)
-    (Approve Leave Request) ..&gt; (Update Leave Balance) : include
-    (Process Payroll Entry) ..&gt; (Verify Status &amp; Version) : include
-```
-#### Class Diagram (MVC Architecture)
-```mermaid
-classDiagram
-    class Employee {
-        +String employeeId
-        +String firstName
-        +String lastName
-        +String email
-        +String role
-        +double baseSalary
-        +String departmentId
-    }
-    class LeaveBalance {
-        +String leaveBalanceId
-        +String employeeId
-        +int annualRemaining
-        +int sickRemaining
-        +int version
-    }
-    class LeaveRequest {
-        +String leaveRequestId
-        +String employeeId
-        +String leaveType
-        +int requestedDays
-        +String status
-        +int version
-    }
-    class AttendanceRecord {
-        +String attendanceId
-        +String employeeId
-        +String date
-        +String status
-    }
-    class PayrollEntry {
-        +String payrollEntryId
-        +String payrollRunId
-        +String employeeId
-        +double baseSalary
-        +double netSalary
-        +String status
-        +int version
-    }
-    class EmployeeRepository {
-        -List~Employee~ employees
-        +loadAll()
-        +findById(String id)
-    }
-    class LeaveRepository {
-        -List~LeaveBalance~ balances
-        -List~LeaveRequest~ requests
-        +approveLeaveNoLock(String requestId)
-        +approveLeaveGlobalLock(String requestId)
-        +approveLeaveRowLock(String requestId)
-        +approveLeaveOptimisticLock(String requestId)
-    }
-    class PayrollRepository {
-        -List~PayrollEntry~ entries
-        +processPayrollNoLock(String entryId)
-        +processPayrollGlobalLock(String entryId)
-        +processPayrollRowLock(String entryId)
-        +processPayrollOptimisticLock(String entryId)
-    }
-    class PayrollController {
-        -EmployeeRepository employeeRepo
-        -LeaveRepository leaveRepo
-        -PayrollRepository payrollRepo
-        +runSimulation(int threadCount, String mechanism)
-    }
-    class MainView {
-        +displayMenu()
-        +displayResults(SimulationReport report)
-    }
-    LeaveRepository --&gt; LeaveBalance
-    LeaveRepository --&gt; LeaveRequest
-    PayrollRepository --&gt; PayrollEntry
-    PayrollController --&gt; EmployeeRepository
-    PayrollController --&gt; LeaveRepository
-    PayrollController --&gt; PayrollRepository
-```
----
-## Verification Plan
-We will verify our data structure, parser accuracy, and synchronization safety through the following tests:
-### Automated Tests
-1. **Round-Trip CSV Parsing Test**:
-   - `DataGenerator` will write all CSVs and immediately load them back, comparing field-by-field values to ensure no precision is lost or data corrupted.
-2. **Concurrency Conflict Tests**:
-   - Spawns 10 threads doing simultaneous updates on the *same* employee's leave balance using the 4 mechanisms, verifying that:
-     - **No Lock** leads to incorrect balances (Wrong Leave Deduction) or multiple payments (Double Payment).
-     - **Global, Row, and Optimistic Locks** guarantee 0% data corruption, with varying performance profiles.
-### Manual Verification
-- We will execute the main simulation menu, select the option to generate files, verify the creation of the 7 CSV files in the project root, and check their line counts using simple terminal checks.
-</t>
   </si>
   <si>
     <t xml:space="preserve">I'll read Schema_Design.md to extract requirements to implement the model and salary logic.
@@ -1100,6 +913,35 @@
   </si>
   <si>
     <t>1. Thay đổi cấu hình dự án                           2. Định nghĩa các ngoại lệ nghiệp vụ tùy chỉnh (Custom Exceptions)                           3. Cài đặt các lớp Controller &amp; View              4. Kiểm thử chất lượng (Unit Testing)</t>
+  </si>
+  <si>
+    <t>Implement processWithSync() và deductWithSync().
+Implement processWithOptimistic() và deductWithOptimistic().
+Thêm version và cơ chế retry với exponential backoff.</t>
+  </si>
+  <si>
+    <t>lm cái này  – SYNCHRONIZED + OPTIMISTIC + Unit Test
+Phụ trách:
+Implement processWithSync() và deductWithSync().
+Implement processWithOptimistic() và deductWithOptimistic().
+Thêm version và cơ chế retry với exponential backoff.
+Viết Unit Test:
+5 threads cùng duyệt lương E001 → chỉ 1 thành công.
+Kiểm tra leave deduction không bị trừ sai.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Đồng bộ và Khóa dữ liệu
+2. Bộ Unit Test được bổ sung
+Duyệt lương E001 với 5 threads đồng thời (
+DoublePaymentTest.java):                          Khấu trừ số ngày nghỉ (Leave Deduction) với 5 threads đồng thời (
+WrongLeaveDeductionTest.java):
+</t>
+  </si>
+  <si>
+    <t>Critical Thinking: chưa biết .
+Contextualization: chưa biết   .
+Creative Synthesis: chưa biết .
+Decision: chưa biết .</t>
   </si>
 </sst>
 </file>
@@ -1771,16 +1613,16 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>255</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1935,11 +1777,9 @@
         <v>245</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>246</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -1961,7 +1801,7 @@
         <v>242</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H5" s="7"/>
     </row>
@@ -1982,10 +1822,10 @@
         <v>243</v>
       </c>
       <c r="F6" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>251</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="H6" s="7"/>
     </row>
@@ -2003,13 +1843,13 @@
         <v>244</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H7" s="7"/>
     </row>
@@ -2024,16 +1864,16 @@
         <v>41</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>259</v>
-      </c>
       <c r="G8" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H8" s="7"/>
     </row>
@@ -2048,16 +1888,16 @@
         <v>37</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>262</v>
-      </c>
       <c r="G9" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H9" s="7"/>
     </row>
@@ -2072,16 +1912,16 @@
         <v>37</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>266</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -2096,16 +1936,16 @@
         <v>41</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H11" s="7"/>
     </row>
@@ -2120,16 +1960,16 @@
         <v>37</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>269</v>
-      </c>
       <c r="G12" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H12" s="7"/>
     </row>
@@ -2144,27 +1984,41 @@
         <v>41</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="G13" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>282</v>
+      </c>
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
